--- a/questionnaire_templates/042_it_hardware_and_software_needs_assessment_form--questionnaire_templates.xlsx
+++ b/questionnaire_templates/042_it_hardware_and_software_needs_assessment_form--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2_years_ago</t>
+          <t>2 years ago</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2_3_years_ago</t>
+          <t>2 3 years ago</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3_4_years_ago</t>
+          <t>3 4 years ago</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4_5_years_ago</t>
+          <t>4 5 years ago</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5_6_years_ago</t>
+          <t>5 6 years ago</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6_7_years_ago</t>
+          <t>6 7 years ago</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7_8_years_ago</t>
+          <t>7 8 years ago</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8_10_years_ago</t>
+          <t>8 10 years ago</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10_years_ago</t>
+          <t>10 years ago</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2_years_ago</t>
+          <t>2 years ago</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2_3_years_ago</t>
+          <t>2 3 years ago</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3_4_years_ago</t>
+          <t>3 4 years ago</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4_5_years_ago</t>
+          <t>4 5 years ago</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5_6_years_ago</t>
+          <t>5 6 years ago</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6_7_years_ago</t>
+          <t>6 7 years ago</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7_8_years_ago</t>
+          <t>7 8 years ago</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8_10_years_ago</t>
+          <t>8 10 years ago</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10_years_ago</t>
+          <t>10 years ago</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IT_Department</t>
+          <t>IT Department</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finance_Department</t>
+          <t>Finance Department</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HR_Department</t>
+          <t>HR Department</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Marketing_Department</t>
+          <t>Marketing Department</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Branch_Office</t>
+          <t>Branch Office</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote_Location</t>
+          <t>Remote Location</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Only_me</t>
+          <t>Only me</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>My_team</t>
+          <t>My team</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>My_team_and_other_teams</t>
+          <t>My team and other teams</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Entire_company</t>
+          <t>Entire company</t>
         </is>
       </c>
     </row>
